--- a/Assets/04. Bakery Factory/AchivementsData.XLSX
+++ b/Assets/04. Bakery Factory/AchivementsData.XLSX
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383855E4-296A-415D-A820-64D9BF7F6449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EDFD3D-E152-4B82-B4F6-C5AF4A841AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12840" yWindow="2370" windowWidth="23310" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>AchivementID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,10 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>첫 실패</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>처음으로 강화를 실패했다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -128,6 +124,88 @@
   </si>
   <si>
     <t>GoldAmount</t>
+  </si>
+  <si>
+    <t>1000Enhance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어느새 천 번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>천 번 강화를 시도했다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>어이쿠 손이 미끄러졌네</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100Fail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자꾸만 손이 미끄러졌네</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기를 100번 파괴했다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000Fail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기 파괴자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기를 1000번 파괴했다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000Enhance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만 번 두드림의 법칙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만 번 강화를 시도했다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lotto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로또 당첨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로또 1등 만큼의 돈을 보유했다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalGold</t>
+  </si>
+  <si>
+    <t>The Rich</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우린 부자가 될거야</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총 수익금이 100억을 넘겼다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -452,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.875" customWidth="1"/>
@@ -504,7 +582,7 @@
         <v>5000000</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -527,7 +605,7 @@
         <v>50000</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -538,19 +616,19 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -558,22 +636,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -581,13 +659,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -596,10 +674,148 @@
         <v>1000000</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>100000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9">
+        <v>1.5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>1.5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11">
+        <v>2500000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12">
+        <v>10000000000</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/04. Bakery Factory/AchivementsData.XLSX
+++ b/Assets/04. Bakery Factory/AchivementsData.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EDFD3D-E152-4B82-B4F6-C5AF4A841AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C36A1E-C1B4-4F88-9A3E-7AC3AEC9F26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12840" yWindow="2370" windowWidth="23310" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
   <si>
     <t>AchivementID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -206,6 +206,32 @@
   <si>
     <t>총 수익금이 100억을 넘겼다</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReachLevel10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여정의 반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10레벨 무기를 획득했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FeatureName</t>
+  </si>
+  <si>
+    <t>집중 강화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockFeature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponLevel</t>
   </si>
 </sst>
 </file>
@@ -530,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.875" customWidth="1"/>
@@ -540,9 +566,10 @@
     <col min="5" max="5" width="17.5" customWidth="1"/>
     <col min="6" max="6" width="18.625" customWidth="1"/>
     <col min="7" max="7" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="22.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -564,8 +591,11 @@
       <c r="G1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -588,7 +618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -611,7 +641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -634,7 +664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -657,7 +687,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -680,7 +710,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -703,7 +733,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -726,7 +756,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -749,7 +779,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -772,7 +802,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -795,7 +825,7 @@
         <v>2500000000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -816,17 +846,46 @@
       </c>
       <c r="G12">
         <v>10000000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D30" xr:uid="{687610E0-D1F6-4BF6-9A0A-FA1E1CECFD8B}">
-      <formula1>"Gold, Weapon, Item, ProbabilityBonus, End"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D30" xr:uid="{687610E0-D1F6-4BF6-9A0A-FA1E1CECFD8B}">
+      <formula1>"Gold, Weapon, Item, ProbabilityBonus, UnlockFeature, End"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F29" xr:uid="{97DDA89E-1FBF-4539-A910-9D6D727D1F0F}">
-      <formula1>"GameStart, GameEnd, ShotEnhance, MaxLevel, FailEnhance, GoldAmount, TotalGold, End"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{EC443BD8-3C12-4E05-86A6-70162CE1D770}">
+      <formula1>"Gold, Weapon, Item, ProbabilityBonus, UnlockFeature, End"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F30" xr:uid="{7B9B82E8-497B-49BD-A8C9-58949D9E8F80}">
+      <formula1>"GameStart, GameEnd, ShotEnhance, WeaponLevel, FailEnhance, GoldAmount, TotalGold, End"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/04. Bakery Factory/AchivementsData.XLSX
+++ b/Assets/04. Bakery Factory/AchivementsData.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C36A1E-C1B4-4F88-9A3E-7AC3AEC9F26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E538FEBF-3D57-4DC7-A2D0-C952169BE428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="77">
   <si>
     <t>AchivementID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,14 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>강화를 시작해보자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 시작</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RewardType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -83,10 +75,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>처음으로 강화를 실패했다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ProbabilityBonus</t>
   </si>
   <si>
@@ -94,10 +82,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>강화를 100번 시도했다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>백번의 두드림</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -134,10 +118,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>천 번 강화를 시도했다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Weapon</t>
   </si>
   <si>
@@ -153,10 +133,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>무기를 100번 파괴했다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1000Fail</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -165,10 +141,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>무기를 1000번 파괴했다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10000Enhance</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,10 +149,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>만 번 강화를 시도했다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Lotto</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -189,10 +157,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>로또 1등 만큼의 돈을 보유했다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TotalGold</t>
   </si>
   <si>
@@ -204,10 +168,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>총 수익금이 100억을 넘겼다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ReachLevel10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -232,13 +192,139 @@
   </si>
   <si>
     <t>WeaponLevel</t>
+  </si>
+  <si>
+    <t>TheMasterSword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마스터 소드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전쟁은 이제 끝날 것이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총 수익금이 100억을 넘겼다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로또 1등 만큼의 돈을 보유했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>만 번 강화를 시도했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기를 1000번 파괴했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기를 100번 파괴했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화를 시작해보자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화를 100번 시도했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>처음으로 강화를 실패했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>천 번 강화를 시도했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockFeature</t>
+  </si>
+  <si>
+    <t>마법 공학 대장간에 오신 걸 환영합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TheMillionaire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백만장자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백만장자가 되었다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득 골드 증가 (10%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득 골드 증가 (20%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Midas touch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미다스의 손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신의 손을 거치면 골드가 되리라.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Three-Sword Style</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼도류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀철을 3개 소지한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break the mood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분위기 전환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13레벨 무기를 획득했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득 골드 증가 (5%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AdditionalGold</t>
+  </si>
+  <si>
+    <t>집중 강화 강화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>확률 + 5%p</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +334,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -274,8 +368,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -556,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.875" customWidth="1"/>
@@ -567,9 +662,10 @@
     <col min="6" max="6" width="18.625" customWidth="1"/>
     <col min="7" max="7" width="15.125" customWidth="1"/>
     <col min="8" max="8" width="22.875" customWidth="1"/>
+    <col min="9" max="9" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -580,22 +676,22 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" t="s">
-        <v>11</v>
-      </c>
       <c r="H1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -603,286 +699,407 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>5000000</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <v>50000</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>1000000</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G6">
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G7">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G8">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E9">
         <v>1.5</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G9">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E10">
         <v>1.5</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G10">
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>2500000000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G12">
         <v>10000000000</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E13">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G13">
         <v>10</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15">
+        <v>1000000000</v>
+      </c>
+      <c r="H15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16">
+        <v>100000000</v>
+      </c>
+      <c r="H16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>5000000</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D30" xr:uid="{687610E0-D1F6-4BF6-9A0A-FA1E1CECFD8B}">
-      <formula1>"Gold, Weapon, Item, ProbabilityBonus, UnlockFeature, End"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{EC443BD8-3C12-4E05-86A6-70162CE1D770}">
-      <formula1>"Gold, Weapon, Item, ProbabilityBonus, UnlockFeature, End"</formula1>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D30" xr:uid="{687610E0-D1F6-4BF6-9A0A-FA1E1CECFD8B}">
+      <formula1>"Gold, Weapon, Item, ProbabilityBonus, UnlockFeature, AdditionalGold, End"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F30" xr:uid="{7B9B82E8-497B-49BD-A8C9-58949D9E8F80}">
       <formula1>"GameStart, GameEnd, ShotEnhance, WeaponLevel, FailEnhance, GoldAmount, TotalGold, End"</formula1>

--- a/Assets/04. Bakery Factory/AchivementsData.XLSX
+++ b/Assets/04. Bakery Factory/AchivementsData.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E538FEBF-3D57-4DC7-A2D0-C952169BE428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12914E4-E4E6-4773-A429-36DEB4B6CFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5850" yWindow="5040" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -202,10 +202,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>전쟁은 이제 끝날 것이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>총 수익금이 100억을 넘겼다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -317,6 +313,10 @@
   </si>
   <si>
     <t>확률 + 5%p</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신이 이뤄낸 것.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -699,7 +699,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -722,7 +722,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -745,7 +745,7 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -768,7 +768,7 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -814,7 +814,7 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
@@ -837,7 +837,7 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -860,7 +860,7 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -906,7 +906,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
@@ -929,10 +929,10 @@
         <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -944,7 +944,7 @@
         <v>10000000000</v>
       </c>
       <c r="H12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -981,10 +981,10 @@
         <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14">
         <v>20</v>
@@ -996,24 +996,24 @@
         <v>20</v>
       </c>
       <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" t="s">
         <v>75</v>
-      </c>
-      <c r="I14" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>60</v>
       </c>
-      <c r="C15" t="s">
-        <v>61</v>
-      </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1025,21 +1025,21 @@
         <v>1000000000</v>
       </c>
       <c r="H15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
         <v>64</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>65</v>
       </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16">
         <v>5</v>
@@ -1051,18 +1051,18 @@
         <v>100000000</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
         <v>67</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -1073,13 +1073,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s">
         <v>70</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>72</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>

--- a/Assets/04. Bakery Factory/AchivementsData.XLSX
+++ b/Assets/04. Bakery Factory/AchivementsData.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12914E4-E4E6-4773-A429-36DEB4B6CFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0C222B-D3DC-4A74-BD0A-6908AC7A3F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5850" yWindow="5040" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="82">
   <si>
     <t>AchivementID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -168,10 +168,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ReachLevel10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>여정의 반</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -317,6 +313,28 @@
   </si>
   <si>
     <t>당신이 이뤄낸 것.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HasItem</t>
+  </si>
+  <si>
+    <t>강화 확률 증가 (1%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HasItemType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Below</t>
+  </si>
+  <si>
+    <t>Sword of Admiral Yi Sun-sin 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -651,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.875" customWidth="1"/>
@@ -663,9 +681,11 @@
     <col min="7" max="7" width="15.125" customWidth="1"/>
     <col min="8" max="8" width="22.875" customWidth="1"/>
     <col min="9" max="9" width="16.625" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -688,10 +708,16 @@
         <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="I1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -699,7 +725,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -714,7 +740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -722,7 +748,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -737,7 +763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -745,7 +771,7 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -760,7 +786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -768,7 +794,7 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -783,7 +809,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -800,13 +826,13 @@
         <v>1000000</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="G6">
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -814,7 +840,7 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
@@ -829,7 +855,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -837,7 +863,7 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -852,7 +878,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -860,7 +886,7 @@
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -875,7 +901,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -883,7 +909,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -898,7 +924,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -906,7 +932,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
@@ -921,7 +947,7 @@
         <v>2500000000</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -929,10 +955,10 @@
         <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -944,76 +970,76 @@
         <v>10000000000</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>39</v>
       </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G13">
         <v>10</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14">
         <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G14">
         <v>20</v>
       </c>
       <c r="H14" t="s">
+        <v>73</v>
+      </c>
+      <c r="K14" t="s">
         <v>74</v>
       </c>
-      <c r="I14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
         <v>58</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>59</v>
       </c>
-      <c r="C15" t="s">
-        <v>60</v>
-      </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1025,21 +1051,21 @@
         <v>1000000000</v>
       </c>
       <c r="H15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
         <v>63</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>64</v>
       </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16">
         <v>5</v>
@@ -1051,18 +1077,18 @@
         <v>100000000</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s">
         <v>66</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>68</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -1070,16 +1096,31 @@
       <c r="E17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
         <v>69</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>70</v>
-      </c>
-      <c r="C18" t="s">
-        <v>71</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -1088,7 +1129,7 @@
         <v>5000000</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G18">
         <v>13</v>
@@ -1097,12 +1138,15 @@
   </sheetData>
   <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D30" xr:uid="{687610E0-D1F6-4BF6-9A0A-FA1E1CECFD8B}">
       <formula1>"Gold, Weapon, Item, ProbabilityBonus, UnlockFeature, AdditionalGold, End"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F30" xr:uid="{7B9B82E8-497B-49BD-A8C9-58949D9E8F80}">
-      <formula1>"GameStart, GameEnd, ShotEnhance, WeaponLevel, FailEnhance, GoldAmount, TotalGold, End"</formula1>
+      <formula1>"GameStart, GameEnd, ShotEnhance, WeaponLevel, FailEnhance, GoldAmount, TotalGold, Below, HasItem, End"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I30" xr:uid="{38185B87-33CC-465C-9E00-D8423A56BFAF}">
+      <formula1>"Weapon, Item, End"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/04. Bakery Factory/AchivementsData.XLSX
+++ b/Assets/04. Bakery Factory/AchivementsData.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0C222B-D3DC-4A74-BD0A-6908AC7A3F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D5E7AB-F348-43A1-8DE5-2A4FC35F5623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5850" yWindow="5040" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="90">
   <si>
     <t>AchivementID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -114,10 +114,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>어느새 천 번</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Weapon</t>
   </si>
   <si>
@@ -145,10 +141,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>만 번 두드림의 법칙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Lotto</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -176,9 +168,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FeatureName</t>
-  </si>
-  <si>
     <t>집중 강화</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -206,14 +195,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>만 번 강화를 시도했다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기를 1000번 파괴했다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>무기를 100번 파괴했다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -230,10 +211,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>천 번 강화를 시도했다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>UnlockFeature</t>
   </si>
   <si>
@@ -304,14 +281,6 @@
     <t>AdditionalGold</t>
   </si>
   <si>
-    <t>집중 강화 강화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>확률 + 5%p</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>당신이 이뤄낸 것.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -327,14 +296,71 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>HasItemType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Below</t>
   </si>
   <si>
     <t>Sword of Admiral Yi Sun-sin 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>집중 강화 강화 (확률 + 5%p)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HighGrade AD</t>
+  </si>
+  <si>
+    <t>ItemRewardAddress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnhancecAnvil</t>
+  </si>
+  <si>
+    <t>해머와 모루를 최대치만큼 강화했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장인도 도구를 가리는 법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HasItemAmount</t>
+  </si>
+  <si>
+    <t>EnhanceGold</t>
+  </si>
+  <si>
+    <t>강화 골드 감소 (5%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AchieveCode</t>
+  </si>
+  <si>
+    <t>GameEnd</t>
+  </si>
+  <si>
+    <t>무기를 50번 파괴했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>천 번 찔린 검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화 중독</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500번 강화를 시도했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000번 강화를 시도했다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -386,9 +412,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -669,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.875" customWidth="1"/>
@@ -679,10 +708,9 @@
     <col min="5" max="5" width="17.5" customWidth="1"/>
     <col min="6" max="6" width="18.625" customWidth="1"/>
     <col min="7" max="7" width="15.125" customWidth="1"/>
-    <col min="8" max="8" width="22.875" customWidth="1"/>
-    <col min="9" max="9" width="16.625" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="11.625" customWidth="1"/>
+    <col min="8" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="17.875" customWidth="1"/>
+    <col min="11" max="11" width="25.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -708,13 +736,13 @@
         <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="I1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -725,7 +753,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -748,7 +776,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -768,10 +796,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -794,19 +822,22 @@
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>17</v>
       </c>
       <c r="G5">
         <v>100</v>
+      </c>
+      <c r="K5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -826,7 +857,7 @@
         <v>1000000</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G6">
         <v>100000</v>
@@ -837,13 +868,13 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
         <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -852,18 +883,18 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
         <v>13</v>
@@ -875,18 +906,18 @@
         <v>18</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
@@ -903,42 +934,42 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
       </c>
       <c r="E10">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
@@ -946,149 +977,149 @@
       <c r="G11">
         <v>2500000000</v>
       </c>
+      <c r="K11" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12">
         <v>10000000000</v>
       </c>
-      <c r="H12" t="s">
-        <v>61</v>
+      <c r="J12" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
         <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
       </c>
       <c r="E13">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G13">
         <v>10</v>
       </c>
-      <c r="H13" t="s">
-        <v>41</v>
+      <c r="K13" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E14">
         <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G14">
         <v>20</v>
       </c>
-      <c r="H14" t="s">
-        <v>73</v>
-      </c>
       <c r="K14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E15">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G15">
         <v>1000000000</v>
       </c>
-      <c r="H15" t="s">
-        <v>60</v>
+      <c r="K15" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E16">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G16">
         <v>100000000</v>
       </c>
-      <c r="H16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
@@ -1097,30 +1128,30 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>3</v>
       </c>
-      <c r="H17" t="s">
-        <v>77</v>
-      </c>
-      <c r="I17" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17">
+      <c r="I17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -1129,24 +1160,50 @@
         <v>5000000</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G18">
         <v>13</v>
       </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19">
+        <v>19</v>
+      </c>
+      <c r="K19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
     </row>
   </sheetData>
   <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D30" xr:uid="{687610E0-D1F6-4BF6-9A0A-FA1E1CECFD8B}">
-      <formula1>"Gold, Weapon, Item, ProbabilityBonus, UnlockFeature, AdditionalGold, End"</formula1>
+      <formula1>"Gold, Weapon, Item, ProbabilityBonus, UnlockFeature, AdditionalGold, EnhanceGold, End"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F30" xr:uid="{7B9B82E8-497B-49BD-A8C9-58949D9E8F80}">
-      <formula1>"GameStart, GameEnd, ShotEnhance, WeaponLevel, FailEnhance, GoldAmount, TotalGold, Below, HasItem, End"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I30" xr:uid="{38185B87-33CC-465C-9E00-D8423A56BFAF}">
-      <formula1>"Weapon, Item, End"</formula1>
+      <formula1>"GameStart, GameEnd, AchieveCode, ShotEnhance, WeaponLevel, FailEnhance, GoldAmount, TotalGold, Below, HasItem, End"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
